--- a/Team-Data/2014-15/3-30-2014-15.xlsx
+++ b/Team-Data/2014-15/3-30-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>0.757</v>
+        <v>0.753</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -688,19 +755,19 @@
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O2" t="n">
         <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>8.6</v>
@@ -709,16 +776,16 @@
         <v>31.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="V2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
@@ -736,10 +803,10 @@
         <v>102.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -802,13 +869,13 @@
         <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J3" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
         <v>8</v>
@@ -876,7 +943,7 @@
         <v>0.327</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P3" t="n">
         <v>20.5</v>
@@ -888,13 +955,13 @@
         <v>11.2</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V3" t="n">
         <v>13.9</v>
@@ -903,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
         <v>5.3</v>
@@ -915,13 +982,13 @@
         <v>18.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
@@ -930,7 +997,7 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -975,25 +1042,25 @@
         <v>5</v>
       </c>
       <c r="AV3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW3" t="n">
         <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1127,7 +1194,7 @@
         <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>20</v>
@@ -1136,13 +1203,13 @@
         <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
@@ -1163,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.425</v>
+        <v>0.431</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1228,34 +1295,34 @@
         <v>84.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="O5" t="n">
         <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
         <v>20.6</v>
@@ -1270,7 +1337,7 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
         <v>18.5</v>
@@ -1279,25 +1346,25 @@
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1324,19 +1391,19 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1509,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1530,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
         <v>25</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1691,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>19</v>
@@ -1700,7 +1767,7 @@
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
@@ -1712,7 +1779,7 @@
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -1721,7 +1788,7 @@
         <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.616</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,49 +1838,49 @@
         <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>9.1</v>
       </c>
       <c r="M8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O8" t="n">
         <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" t="n">
         <v>3.9</v>
@@ -1825,13 +1892,13 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1876,10 +1943,10 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1903,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2046,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2076,7 +2143,7 @@
         <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2258,7 +2325,7 @@
         <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2416,13 +2483,13 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2434,10 +2501,10 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.671</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,28 +2566,28 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
       </c>
       <c r="L12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R12" t="n">
         <v>11.8</v>
@@ -2547,28 +2614,28 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
         <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>26</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="n">
         <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2765,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2780,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
@@ -2810,13 +2877,13 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" t="n">
         <v>5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2980,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3030,55 +3097,55 @@
         <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.278</v>
+        <v>0.264</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3087,7 +3154,7 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.8</v>
@@ -3096,16 +3163,16 @@
         <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,25 +3184,25 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM15" t="n">
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
@@ -3147,10 +3214,10 @@
         <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>11</v>
@@ -3165,13 +3232,13 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3233,16 +3300,16 @@
         <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="N16" t="n">
         <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P16" t="n">
         <v>22.9</v>
@@ -3269,7 +3336,7 @@
         <v>8.6</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
         <v>5.3</v>
@@ -3284,19 +3351,19 @@
         <v>98.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>6</v>
@@ -3305,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3317,10 +3384,10 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
@@ -3329,7 +3396,7 @@
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
         <v>17</v>
@@ -3347,22 +3414,22 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3523,7 +3590,7 @@
         <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
@@ -3541,7 +3608,7 @@
         <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
         <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.457</v>
@@ -3603,7 +3670,7 @@
         <v>18.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O18" t="n">
         <v>16.4</v>
@@ -3612,13 +3679,13 @@
         <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R18" t="n">
         <v>10.6</v>
       </c>
       <c r="S18" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T18" t="n">
         <v>42.1</v>
@@ -3630,13 +3697,13 @@
         <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
         <v>22.2</v>
@@ -3645,13 +3712,13 @@
         <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
         <v>18</v>
@@ -3681,7 +3748,7 @@
         <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3699,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3708,16 +3775,16 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3726,7 +3793,7 @@
         <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3755,37 +3822,37 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J19" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O19" t="n">
         <v>19.7</v>
@@ -3803,7 +3870,7 @@
         <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U19" t="n">
         <v>21.7</v>
@@ -3824,16 +3891,16 @@
         <v>19.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,16 +3912,16 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>5</v>
@@ -3881,13 +3948,13 @@
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU19" t="n">
         <v>15</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>9</v>
@@ -3899,7 +3966,7 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -3937,67 +4004,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O20" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,16 +4094,16 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4045,16 +4112,16 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4221,13 +4288,13 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
@@ -4448,10 +4515,10 @@
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.301</v>
+        <v>0.297</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.35</v>
@@ -4519,22 +4586,22 @@
         <v>14.1</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4546,22 +4613,22 @@
         <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,10 +4643,10 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4615,16 +4682,16 @@
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J24" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.409</v>
@@ -4698,25 +4765,25 @@
         <v>0.323</v>
       </c>
       <c r="O24" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P24" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.669</v>
+        <v>0.671</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
         <v>31.4</v>
       </c>
       <c r="T24" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
         <v>17.9</v>
@@ -4725,25 +4792,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
         <v>24</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
         <v>86.2</v>
@@ -4871,34 +4938,34 @@
         <v>0.454</v>
       </c>
       <c r="L25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O25" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P25" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T25" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V25" t="n">
         <v>15.3</v>
@@ -4907,28 +4974,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.5</v>
+        <v>103.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4949,31 +5016,31 @@
         <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM25" t="n">
         <v>9</v>
       </c>
       <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
         <v>18</v>
       </c>
-      <c r="AO25" t="n">
-        <v>20</v>
-      </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS25" t="n">
         <v>13</v>
       </c>
-      <c r="AS25" t="n">
-        <v>14</v>
-      </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
@@ -4994,13 +5061,13 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5096,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" t="n">
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>0.658</v>
+        <v>0.653</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J26" t="n">
         <v>85.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M26" t="n">
         <v>27.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O26" t="n">
         <v>15.8</v>
       </c>
       <c r="P26" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="R26" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="T26" t="n">
         <v>45.9</v>
@@ -5095,22 +5162,22 @@
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.6</v>
+        <v>102.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5137,10 +5204,10 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
         <v>28</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5232,7 +5299,7 @@
         <v>80.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
         <v>5.5</v>
@@ -5241,28 +5308,28 @@
         <v>16.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O27" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="P27" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T27" t="n">
         <v>44.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
         <v>16.5</v>
@@ -5280,22 +5347,22 @@
         <v>20.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
         <v>14</v>
@@ -5352,7 +5419,7 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
         <v>16</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.639</v>
+        <v>0.644</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,22 +5478,22 @@
         <v>38.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
         <v>21.8</v>
@@ -5435,10 +5502,10 @@
         <v>0.777</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
         <v>43.7</v>
@@ -5447,19 +5514,19 @@
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA28" t="n">
         <v>19.9</v>
@@ -5468,19 +5535,19 @@
         <v>102.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF28" t="n">
         <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5501,34 +5568,34 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5537,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.595</v>
+        <v>0.589</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5608,7 +5675,7 @@
         <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
         <v>24.8</v>
@@ -5623,7 +5690,7 @@
         <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U29" t="n">
         <v>20.8</v>
@@ -5635,25 +5702,25 @@
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA29" t="n">
         <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
       <c r="AC29" t="n">
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,7 +5732,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5677,7 +5744,7 @@
         <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5701,7 +5768,7 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
         <v>21</v>
@@ -5722,13 +5789,13 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -5757,52 +5824,52 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J30" t="n">
         <v>79</v>
       </c>
       <c r="K30" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O30" t="n">
         <v>16.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.723</v>
+        <v>0.721</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T30" t="n">
         <v>43.7</v>
@@ -5820,22 +5887,22 @@
         <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
@@ -5844,7 +5911,7 @@
         <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5868,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP30" t="n">
         <v>12</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
         <v>30</v>
@@ -5892,25 +5959,25 @@
         <v>24</v>
       </c>
       <c r="AW30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA30" t="n">
         <v>23</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>13</v>
@@ -6053,7 +6120,7 @@
         <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
@@ -6062,7 +6129,7 @@
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6071,13 +6138,13 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-30-2014-15</t>
+          <t>2015-03-30</t>
         </is>
       </c>
     </row>
